--- a/docs/範例_使用者帳號管理_批次刪除.xlsx
+++ b/docs/範例_使用者帳號管理_批次刪除.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\campus-toolkit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0352D7F0-4E70-4343-B281-E30ADA6C054D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E67AF44-B592-4D67-9515-815D68947450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{0F7DB9C0-03AC-4E98-ACB7-4234628B04E2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>電子郵件地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,13 +35,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fake02@fake.edu.tw</t>
-  </si>
-  <si>
     <t>fake03@fake.edu.tw</t>
   </si>
   <si>
-    <t>fake04@fake.edu.tw</t>
+    <t>帳號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fake02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fake04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fake05@fake.edu.tw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -87,8 +97,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -405,35 +418,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0F4001-4939-4474-861F-107A3544EAD0}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
